--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.23758289373087</v>
+        <v>7.838607220231266</v>
       </c>
       <c r="D2" t="n">
-        <v>47.34260967856058</v>
+        <v>7.693174072766095</v>
       </c>
       <c r="E2" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F2" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.91808930059966</v>
+        <v>8.599189511347445</v>
       </c>
       <c r="D3" t="n">
-        <v>52.87347944456137</v>
+        <v>8.591940409741223</v>
       </c>
       <c r="E3" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F3" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.51163031526078</v>
+        <v>3.658139926229877</v>
       </c>
       <c r="D4" t="n">
-        <v>21.3572976022216</v>
+        <v>3.470560860361009</v>
       </c>
       <c r="E4" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F4" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.67990516232518</v>
+        <v>2.060484588877843</v>
       </c>
       <c r="D5" t="n">
-        <v>11.09759096467273</v>
+        <v>1.803358531759319</v>
       </c>
       <c r="E5" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F5" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.65360454648511</v>
+        <v>3.518710738803831</v>
       </c>
       <c r="D6" t="n">
-        <v>21.19467938834473</v>
+        <v>3.444135400606018</v>
       </c>
       <c r="E6" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F6" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.21633696073473</v>
+        <v>9.135154756119395</v>
       </c>
       <c r="D7" t="n">
-        <v>14.13211846684516</v>
+        <v>2.296469250862339</v>
       </c>
       <c r="E7" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F7" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.71169118159487</v>
+        <v>8.890649817009168</v>
       </c>
       <c r="D8" t="n">
-        <v>8.508014609227642</v>
+        <v>1.382552373999492</v>
       </c>
       <c r="E8" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F8" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.19836323863412</v>
+        <v>2.144734026278045</v>
       </c>
       <c r="D9" t="n">
-        <v>13.00647360184748</v>
+        <v>2.113551960300215</v>
       </c>
       <c r="E9" t="n">
-        <v>18.17275870620011</v>
+        <v>2.953073289757517</v>
       </c>
       <c r="F9" t="n">
-        <v>15.87978989340029</v>
+        <v>2.580465857677548</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
